--- a/TestCases_Docs/CustomerOrders_TestCases.xlsx
+++ b/TestCases_Docs/CustomerOrders_TestCases.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FOTOH_COMPU\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F38DBA-3BA6-4A77-B96A-470891F89130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066265FF-41EE-4635-8433-28E8D639537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerOrders_Tcs" sheetId="2" r:id="rId1"/>
+    <sheet name="CustomerOrder Execution" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>El-Gohary</t>
   </si>
@@ -118,6 +117,19 @@
   </si>
   <si>
     <t>TesTCASE ID</t>
+  </si>
+  <si>
+    <t>passed</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>order details appear such 
+id,price, date</t>
+  </si>
+  <si>
+    <t>prevoius orders exist</t>
   </si>
 </sst>
 </file>
@@ -273,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -305,6 +317,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -588,27 +603,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CF0651-39A0-4191-B4B4-E9DA21D2025A}">
   <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="21.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>26</v>
       </c>
@@ -667,7 +682,7 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
@@ -731,4 +746,154 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4180117E-C74C-4A39-B550-D5041FEAA423}">
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.26953125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.90625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" spans="1:26" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2" xr:uid="{038FB001-E538-47CA-8023-42CE06DC47F1}">
+      <formula1>"valid,invalid"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>